--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856177</v>
       </c>
       <c r="B2" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135856173</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135856174</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135856175</v>
       </c>
       <c r="B5" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856177</v>
       </c>
       <c r="B2" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135856173</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135856174</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135856173</v>
+        <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>92086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718870</v>
+        <v>718738</v>
       </c>
       <c r="R3" t="n">
-        <v>7148888</v>
+        <v>7149024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -888,13 +888,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135856173</t>
+          <t>https://artportalen.se/Sighting/136194310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135856174</v>
+        <v>135856173</v>
       </c>
       <c r="B4" t="n">
         <v>79444</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718832</v>
+        <v>718870</v>
       </c>
       <c r="R4" t="n">
-        <v>7148867</v>
+        <v>7148888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,38 +995,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135856174</t>
+          <t>https://artportalen.se/Sighting/135856173</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135856175</v>
+        <v>135856174</v>
       </c>
       <c r="B5" t="n">
-        <v>58086</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718822</v>
+        <v>718832</v>
       </c>
       <c r="R5" t="n">
-        <v>7148967</v>
+        <v>7148867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,6 +1101,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135856174</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135856175</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gladaberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>718822</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7148967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135856175</t>
         </is>
@@ -1112,6 +1219,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856177</v>
       </c>
       <c r="B2" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135856173</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135856174</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135856175</v>
       </c>
       <c r="B6" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856177</v>
       </c>
       <c r="B2" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135856173</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135856174</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135856175</v>
       </c>
       <c r="B6" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856177</v>
       </c>
       <c r="B2" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135856173</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135856174</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135856175</v>
       </c>
       <c r="B6" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
